--- a/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
+++ b/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -949,12 +949,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2938,12 +2938,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -3510,12 +3510,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I78" s="2"/>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3845,12 +3845,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I89" s="2"/>
@@ -4108,12 +4108,12 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4456,26 +4456,26 @@
       <c r="A7" s="0"/>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4488,7 +4488,7 @@
       <c r="K7" s="8"/>
       <c r="L7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="10"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O10" s="10"/>
@@ -4768,7 +4768,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="N13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>

--- a/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
+++ b/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4155,94 +4196,94 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">노래가락</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">회</t>
         </is>
@@ -4250,60 +4291,60 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="L4" s="21"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">광</t>
         </is>
@@ -4311,67 +4352,67 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">옹</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="23"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">외</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="23"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="N5" s="18" t="inlineStr">
+      <c r="N5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O5" s="12" t="inlineStr">
+      <c r="O5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4379,74 +4420,74 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">외</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">앉</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="O6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4454,51 +4495,51 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="E7" s="22"/>
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="G7" s="27"/>
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="27"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="K7" s="22"/>
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="27"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4506,73 +4547,73 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O8" s="9" t="inlineStr">
+      <c r="O8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -4580,66 +4621,66 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="23"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="23"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">옷</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="O9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4647,118 +4688,118 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="26"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="26"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O10" s="10"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="22"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="22"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -4766,63 +4807,63 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="23"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="23"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O12" s="9" t="inlineStr">
+      <c r="O12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -4830,112 +4871,112 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">‹</t>
         </is>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="J13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="L13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 㳞仲</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어물</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
+      <c r="O13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="M14" s="26"/>
+      <c r="N14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
 仲姑</t>
         </is>
       </c>
-      <c r="O14" s="13" t="inlineStr">
+      <c r="O14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4943,52 +4984,52 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="G15" s="27"/>
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">걸</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 㳞潢</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">언</t>
         </is>
       </c>
-      <c r="N15" s="17"/>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="N15" s="21"/>
+      <c r="O15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4996,99 +5037,99 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="B16" s="21"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="G16" s="23"/>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J16" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">‹</t>
         </is>
       </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="K16" s="25"/>
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="N16" s="18" t="inlineStr">
+      <c r="N16" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">‹</t>
         </is>
       </c>
-      <c r="O16" s="12"/>
+      <c r="O16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="23"/>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="I17" s="23"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="9"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="23"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="10"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
+++ b/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
@@ -4175,26 +4175,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="23" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -4350,7 +4350,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="23"/>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
       <c r="K10" s="26"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="26" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="O10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="24" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
       <c r="E12" s="23"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="23"/>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M14" s="26"/>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="O16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5114,7 +5114,7 @@
       <c r="N17" s="21"/>
       <c r="O17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>

--- a/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
+++ b/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
@@ -1101,12 +1101,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I15" s="3"/>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I43" s="3"/>
@@ -3769,12 +3769,12 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I84" s="3"/>
@@ -4875,7 +4875,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E13" s="25"/>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="J16" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K16" s="25"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="N16" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">‹</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O16" s="25"/>

--- a/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
+++ b/sheets/민요/검수/노래가락 (채보3) 노래가락.xlsx
@@ -4918,7 +4918,8 @@
       </c>
       <c r="M13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">어물</t>
+          <t xml:space="preserve">어
+물</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
